--- a/WorkBot/refactor-experimental/data/transfer_archive/Bakery_Downtown_20260213.xlsx
+++ b/WorkBot/refactor-experimental/data/transfer_archive/Bakery_Downtown_20260213.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\refactor-experimental\data\transfers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\refactor-experimental\data\transfer_archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DC9982-80E9-419D-BC54-F7C8E72EBBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4EBA06-B845-4718-BD3B-D7BC41D26215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="3330" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Lid - Soup (6/16 oz)</t>
   </si>
   <si>
-    <t>Celsius - Vibe Peach, Tropical, Arctic</t>
-  </si>
-  <si>
     <t>Apple Cider (Gal)</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>Kilogram Chai Concentrate</t>
   </si>
   <si>
-    <t>Tea Bags - Earl Grey (Twinings)</t>
-  </si>
-  <si>
     <t>Tea Bags - Lemon Ginger (Twinings)</t>
   </si>
   <si>
@@ -89,9 +83,6 @@
   </si>
   <si>
     <t>Urnex - Rinza</t>
-  </si>
-  <si>
-    <t>Chobani - Drinkable Yogurt (protein mixed berry)</t>
   </si>
 </sst>
 </file>
@@ -431,10 +422,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -447,15 +439,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
         <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -463,7 +455,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -471,7 +463,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -479,7 +471,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -490,7 +482,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -503,7 +495,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -511,7 +503,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -519,7 +511,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -527,15 +519,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -543,7 +535,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -551,10 +543,10 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -570,7 +562,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -578,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -594,34 +586,13 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B20">
+    <sortCondition ref="A2:A20"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>